--- a/reports/Sales_Report.xlsx
+++ b/reports/Sales_Report.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -471,51 +471,76 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-07 12:54:32.0700000</t>
+          <t>2026-10-08 11:55:35.4133333</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>187</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:23.6700000</t>
+          <t>2026-10-07 12:54:32.0700000</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>400</v>
+        <v>170</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:53:23.6700000</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>472</v>
       </c>
     </row>

--- a/reports/Sales_Report.xlsx
+++ b/reports/Sales_Report.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -471,77 +471,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-08 11:55:35.4133333</t>
+          <t>2026-10-09 15:36:55.0466667</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-10-07 12:54:32.0700000</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>170</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-10-07 10:53:23.6700000</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>472</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>
